--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-integration-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-integration-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Theo quy chuẩn REST API, PUT thay thế toàn bộ đối tượng bằng payload mới gửi lên (nếu thiếu trường sẽ bị set NULL hoặc default). PATCH cập nhật cục bộ chỉ những trường được gửi lên.</v>
       </c>
       <c r="F2" t="str">
+        <v>PUT chỉ dùng cho dữ liệu số; PATCH chỉ dùng cho dữ liệu chuỗi văn bản — giới hạn kiểu dữ liệu</v>
+      </c>
+      <c r="G2" t="str">
+        <v>PUT gửi dữ liệu qua URL; PATCH gửi dữ liệu ẩn dưới thân Request Body — phương thức gửi nhận</v>
+      </c>
+      <c r="H2" t="str">
         <v>PUT dùng để cập nhật ghi đè toàn bộ tài nguyên; PATCH dùng để cập nhật một phần (chỉ các trường thay đổi) của tài nguyên — ghi đè vs cập nhật một phần</v>
-      </c>
-      <c r="G2" t="str">
-        <v>PUT chỉ dùng cho dữ liệu số; PATCH chỉ dùng cho dữ liệu chuỗi văn bản — giới hạn kiểu dữ liệu</v>
-      </c>
-      <c r="H2" t="str">
-        <v>PUT gửi dữ liệu qua URL; PATCH gửi dữ liệu ẩn dưới thân Request Body — phương thức gửi nhận</v>
       </c>
       <c r="I2" t="str">
         <v>PUT bắt buộc phải có chứng chỉ bảo mật SSL; PATCH có thể chạy qua giao thức HTTP thường — yêu cầu bảo mật</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Hệ quản trị CSDL quan hệ (RDBMS) không hỗ trợ trực tiếp quan hệ n-n ở tầng vật lý. BA/Designer phải phân rã quan hệ n-n thành hai quan hệ 1-n thông qua một bảng trung gian.</v>
       </c>
       <c r="F3" t="str">
+        <v>Không thể biểu diễn được quan hệ nhiều nhiều trong cơ sở dữ liệu quan hệ vật lý — giới hạn RDBMS</v>
+      </c>
+      <c r="G3" t="str">
         <v>Tạo ra một bảng trung gian (Junction/Association Table) chứa hai khóa ngoại trỏ tới khóa chính của hai bảng gốc — bảng trung gian liên kết</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Vẽ một đường nối trực tiếp giữa hai bảng và ghi ký hiệu n-n ở hai đầu — ký hiệu sơ đồ</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Thêm trực tiếp một mảng (Array) các khóa ngoại vào trong một cột của bảng đối tác — lưu trữ dạng mảng</v>
       </c>
-      <c r="I3" t="str">
-        <v>Không thể biểu diễn được quan hệ nhiều nhiều trong cơ sở dữ liệu quan hệ vật lý — giới hạn RDBMS</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         <v>Một API Spec hoàn chỉnh phải chứa đầy đủ thông tin kỹ thuật: URL nhận request, phương thức gọi, cấu trúc dữ liệu gửi đi (Request), dữ liệu nhận về khi thành công/thất bại (Response) để dev/test làm việc độc lập.</v>
       </c>
       <c r="F5" t="str">
+        <v>Màu sắc của nút bấm gọi API hiển thị trên màn hình ứng dụng di động — thiết kế nút bấm giao diện</v>
+      </c>
+      <c r="G5" t="str">
         <v>Endpoint URL, HTTP Method, Request Headers, Request Body Schema, Response Headers, Response Body Schema và Error Codes — đặc tả chi tiết API</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Số lượng dòng code cần viết để xử lý logic bên trong API đó — độ dài mã nguồn</v>
       </c>
       <c r="H5" t="str">
         <v>Tên và email của lập trình viên chịu trách nhiệm viết code cho API đó — nhân sự phát triển</v>
       </c>
       <c r="I5" t="str">
-        <v>Màu sắc của nút bấm gọi API hiển thị trên màn hình ứng dụng di động — thiết kế nút bấm giao diện</v>
+        <v>Số lượng dòng code cần viết để xử lý logic bên trong API đó — độ dài mã nguồn</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Chuẩn hóa dữ liệu (Normalization) giúp phân rã các bảng to thành bảng nhỏ logic hơn để tránh các bất thường khi thêm/sửa/xóa dữ liệu (Anomalies) và tiết kiệm không gian lưu trữ.</v>
       </c>
       <c r="F6" t="str">
+        <v>Tăng tốc độ hiển thị giao diện trang web lên dưới 1 giây — tối ưu giao diện</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Tự động sao lưu dữ liệu dự phòng từ máy chủ chính sang máy chủ phụ hàng ngày — sao lưu dữ liệu</v>
+      </c>
+      <c r="H6" t="str">
         <v>Giảm thiểu tối đa sự trùng lặp dữ liệu (Redundancy) và đảm bảo tính nhất quán của dữ liệu (Data Integrity) — tối ưu hóa cấu trúc</v>
       </c>
-      <c r="G6" t="str">
-        <v>Tăng tốc độ hiển thị giao diện trang web lên dưới 1 giây — tối ưu giao diện</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Mã hóa toàn bộ các bảng dữ liệu để hacker không thể đọc trộm thông tin — bảo mật dữ liệu</v>
       </c>
-      <c r="I6" t="str">
-        <v>Tự động sao lưu dữ liệu dự phòng từ máy chủ chính sang máy chủ phụ hàng ngày — sao lưu dữ liệu</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Mã 401 Unauthorized cho biết request cần được xác thực danh tính (Authentication). Tránh nhầm với 403 Forbidden (đã biết danh tính nhưng bị cấm truy cập).</v>
       </c>
       <c r="F7" t="str">
-        <v>Yêu cầu thiếu thông tin xác thực hợp lệ (như token hết hạn, sai username/password) — lỗi xác thực danh tính</v>
+        <v>Tham số gửi lên trong Request Body bị sai định dạng dữ liệu quy định — lỗi cú pháp request</v>
       </c>
       <c r="G7" t="str">
         <v>Tài khoản đã xác thực đúng nhưng không có quyền truy cập vào tài nguyên này — lỗi phân quyền truy cập</v>
       </c>
       <c r="H7" t="str">
-        <v>Tham số gửi lên trong Request Body bị sai định dạng dữ liệu quy định — lỗi cú pháp request</v>
+        <v>Yêu cầu thiếu thông tin xác thực hợp lệ (như token hết hạn, sai username/password) — lỗi xác thực danh tính</v>
       </c>
       <c r="I7" t="str">
         <v>Máy chủ cơ sở dữ liệu của hệ thống đang bị quá tải và không phản hồi — lỗi quá tải máy chủ</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Webhook là một API ngược. Thay vì hệ thống đích liên tục hỏi (polling) mất tài nguyên, hệ thống nguồn sẽ chủ động gọi API của hệ thống đích để thông báo khi có sự kiện mới (như có giao dịch mới).</v>
       </c>
       <c r="F8" t="str">
+        <v>Khi hệ thống đích phải liên tục gửi request sau mỗi 5 giây để kiểm tra xem hệ thống nguồn có gì mới không — cơ chế polling</v>
+      </c>
+      <c r="G8" t="str">
         <v>Khi hệ thống nguồn muốn tự động đẩy thông báo sự kiện (Event-driven) sang hệ thống đích ngay khi có dữ liệu mới phát sinh — đẩy dữ liệu chủ động</v>
       </c>
-      <c r="G8" t="str">
-        <v>Khi hệ thống đích phải liên tục gửi request sau mỗi 5 giây để kiểm tra xem hệ thống nguồn có gì mới không — cơ chế polling</v>
-      </c>
       <c r="H8" t="str">
+        <v>Khi cần thiết kế lại giao diện người dùng theo chuẩn responsive di động — responsive giao diện</v>
+      </c>
+      <c r="I8" t="str">
         <v>Khi cần mã hóa toàn bộ dữ liệu truyền tải qua đường truyền mạng internet — bảo mật đường truyền</v>
       </c>
-      <c r="I8" t="str">
-        <v>Khi cần thiết kế lại giao diện người dùng theo chuẩn responsive di động — responsive giao diện</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>Quy tắc chuyển đổi dữ liệu (Transformation Rules) để ánh xạ tương ứng: 0 thành "PENDING", 1 thành "PROCESSING", 2 thành "COMPLETED" — quy tắc chuyển đổi giá trị</v>
       </c>
       <c r="G9" t="str">
+        <v>Đề xuất xóa bỏ trường trạng thái đơn hàng để không cần thực hiện ánh xạ nữa — loại bỏ trường dữ liệu</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Yêu cầu khách hàng tự nhập tay chuyển đổi dữ liệu khi chạy hệ thống mới — chuyển đổi thủ công</v>
+      </c>
+      <c r="I9" t="str">
         <v>Yêu cầu hệ thống mới sửa lại code để lưu giá trị 0, 1, 2 giống hệt hệ thống cũ — sửa đổi hệ thống mới</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Đề xuất xóa bỏ trường trạng thái đơn hàng để không cần thực hiện ánh xạ nữa — loại bỏ trường dữ liệu</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Yêu cầu khách hàng tự nhập tay chuyển đổi dữ liệu khi chạy hệ thống mới — chuyển đổi thủ công</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>IPN là cơ chế gọi ngầm (Server-to-Server) giữa cổng thanh toán và máy chủ của bạn. Nếu khách hàng thanh toán xong mà tắt trình duyệt trước khi redirect về web, IPN vẫn đảm bảo server nhận được thông tin để cập nhật trạng thái đơn hàng thành "Đã thanh toán".</v>
       </c>
       <c r="F10" t="str">
+        <v>Để tự động trừ tiền trong tài khoản ngân hàng của khách hàng mà không cần mật khẩu OTP — trừ tiền tự động</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Để vẽ lại sơ đồ trang web bán hàng của đối tác theo tông màu thương hiệu của cổng thanh toán — đồng bộ giao diện</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Để tăng tốc độ tải trang thanh toán lên nhanh gấp đôi so với bình thường — tăng tốc tải trang</v>
+      </c>
+      <c r="I10" t="str">
         <v>Để đảm bảo hệ thống cập nhật đúng trạng thái đơn hàng của khách hàng ngay cả khi trình duyệt của khách hàng bị đóng hoặc mất kết nối đột ngột — cập nhật trạng thái tin cậy</v>
       </c>
-      <c r="G10" t="str">
-        <v>Để tự động trừ tiền trong tài khoản ngân hàng của khách hàng mà không cần mật khẩu OTP — trừ tiền tự động</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Để vẽ lại sơ đồ trang web bán hàng của đối tác theo tông màu thương hiệu của cổng thanh toán — đồng bộ giao diện</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Để tăng tốc độ tải trang thanh toán lên nhanh gấp đôi so với bình thường — tăng tốc tải trang</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Primary Key xác định duy nhất thực thể trong bảng và không được NULL. Unique Key đảm bảo dữ liệu trong cột không trùng lặp (ví dụ: Số điện thoại, Email) nhưng chấp nhận giá trị NULL (ở một số hệ quản trị CSDL).</v>
       </c>
       <c r="F11" t="str">
+        <v>Primary Key tự động mã hóa dữ liệu; Unique Key tự động xóa dữ liệu trùng lặp — hành vi tự động</v>
+      </c>
+      <c r="G11" t="str">
         <v>Bảng chỉ có duy nhất 1 Primary Key và giá trị không được NULL; nhưng có thể có nhiều Unique Key và chấp nhận giá trị NULL — ràng buộc khóa</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Primary Key dùng để liên kết bảng; Unique Key chỉ dùng để hiển thị dữ liệu ra màn hình — vai trò khóa</v>
       </c>
       <c r="H11" t="str">
         <v>Primary Key bắt buộc phải là kiểu số nguyên; Unique Key bắt buộc phải là kiểu chuỗi văn bản — kiểu dữ liệu khóa</v>
       </c>
       <c r="I11" t="str">
-        <v>Primary Key tự động mã hóa dữ liệu; Unique Key tự động xóa dữ liệu trùng lặp — hành vi tự động</v>
+        <v>Primary Key dùng để liên kết bảng; Unique Key chỉ dùng để hiển thị dữ liệu ra màn hình — vai trò khóa</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
